--- a/excel_files/4.2.2.1.xlsx
+++ b/excel_files/4.2.2.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A9F263-6BBA-42C8-900F-AB1F59FCC67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -55,9 +56,6 @@
     <t xml:space="preserve"> г.Ош</t>
   </si>
   <si>
-    <t>4.2.2.1а Охват детей дошкольным образованием</t>
-  </si>
-  <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
   <si>
@@ -67,9 +65,6 @@
     <t>Items</t>
   </si>
   <si>
-    <t>4.2.2.1a Coverage of children in preschool education</t>
-  </si>
-  <si>
     <t>(as a percentage of the corresponding age group of 1-6 years)</t>
   </si>
   <si>
@@ -142,19 +137,25 @@
     <t>Osh city</t>
   </si>
   <si>
-    <t>4.2.2.1а Балдарды мектепке чейин билим берүү менен камтуу</t>
-  </si>
-  <si>
     <t>urban</t>
   </si>
   <si>
     <t>rural</t>
+  </si>
+  <si>
+    <t>4.2.2.1 Доля детей в возрасте до шести лет, которые получают дошкольное образование</t>
+  </si>
+  <si>
+    <t>4.2.2.1 Proportion of children under six years of age who receive pre-primary education</t>
+  </si>
+  <si>
+    <t>4.2.2.1 Алты жашка чейинки мектепке чейинки билим берүү алган балдардын үлүшү</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -306,37 +307,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal_PPI" xfId="1"/>
+    <cellStyle name="Normal_PPI" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный_ССП Социальный" xfId="2"/>
+    <cellStyle name="Обычный_ССП Социальный" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -352,9 +353,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -392,9 +393,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -429,7 +430,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -464,7 +465,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -637,37 +638,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="34" style="2" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="C1" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -678,16 +679,17 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="12"/>
+    </row>
+    <row r="4" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="D4" s="6">
         <v>2013</v>
@@ -722,16 +724,19 @@
       <c r="N4" s="10">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O4" s="10">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" s="8">
         <v>17.5</v>
@@ -766,16 +771,19 @@
       <c r="N5" s="22">
         <v>28.34784779265912</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O5" s="11">
+        <v>32.299999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D6" s="2">
         <v>31.6</v>
@@ -810,16 +818,19 @@
       <c r="N6" s="23">
         <v>39.999446500300472</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O6" s="12">
+        <v>38.122910127633112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2">
         <v>10.8</v>
@@ -854,16 +865,19 @@
       <c r="N7" s="23">
         <v>23.198557483143556</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O7" s="12">
+        <v>28.781913406972649</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="8">
         <v>16.100000000000001</v>
@@ -898,16 +912,19 @@
       <c r="N8" s="22">
         <v>27.597876990321573</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O8" s="11">
+        <v>31.083564089956262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2">
         <v>33.299999999999997</v>
@@ -942,16 +959,19 @@
       <c r="N9" s="23">
         <v>47.175678010018999</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O9" s="12">
+        <v>38.840238748747439</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2">
         <v>10.199999999999999</v>
@@ -986,16 +1006,19 @@
       <c r="N10" s="23">
         <v>22.17579894112394</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O10" s="12">
+        <v>27.806512175817705</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="8">
         <v>15.2</v>
@@ -1030,16 +1053,19 @@
       <c r="N11" s="22">
         <v>24.100104034215697</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O11" s="11">
+        <v>27.793379899666355</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2">
         <v>27.4</v>
@@ -1074,16 +1100,19 @@
       <c r="N12" s="23">
         <v>38.296287676015361</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O12" s="12">
+        <v>31.275528484414188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2">
         <v>10.3</v>
@@ -1118,16 +1147,19 @@
       <c r="N13" s="23">
         <v>19.410249509822766</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O13" s="12">
+        <v>26.039486031906446</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" s="8">
         <v>17.399999999999999</v>
@@ -1162,16 +1194,19 @@
       <c r="N14" s="22">
         <v>30.400174646089773</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O14" s="11">
+        <v>34.493449169761085</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2">
         <v>34.200000000000003</v>
@@ -1206,16 +1241,19 @@
       <c r="N15" s="23">
         <v>44.562134629854725</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O15" s="12">
+        <v>46.24464087228074</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D16" s="2">
         <v>9.4</v>
@@ -1250,16 +1288,19 @@
       <c r="N16" s="23">
         <v>24.612036336109007</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O16" s="12">
+        <v>28.681379093693554</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" s="8">
         <v>19.600000000000001</v>
@@ -1294,16 +1335,19 @@
       <c r="N17" s="22">
         <v>39.266683582846994</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O17" s="11">
+        <v>43.24891212472216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2">
         <v>32.6</v>
@@ -1338,16 +1382,19 @@
       <c r="N18" s="23">
         <v>54.818496110630946</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O18" s="12">
+        <v>62.911684497587586</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D19" s="2">
         <v>17.5</v>
@@ -1382,16 +1429,19 @@
       <c r="N19" s="23">
         <v>36.591078066914498</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O19" s="12">
+        <v>39.799823373564905</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" s="8">
         <v>11.6</v>
@@ -1426,16 +1476,19 @@
       <c r="N20" s="22">
         <v>23.890520476423561</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O20" s="11">
+        <v>29.227267837833249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2">
         <v>15</v>
@@ -1470,16 +1523,19 @@
       <c r="N21" s="23">
         <v>16.93085228577992</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O21" s="12">
+        <v>16.299842372584507</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D22" s="2">
         <v>11.4</v>
@@ -1514,16 +1570,19 @@
       <c r="N22" s="23">
         <v>24.386979772654026</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O22" s="12">
+        <v>30.615533152773601</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D23" s="8">
         <v>14.4</v>
@@ -1558,16 +1617,19 @@
       <c r="N23" s="22">
         <v>28.919699950811605</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O23" s="11">
+        <v>33.185588551890078</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2">
         <v>49.4</v>
@@ -1602,16 +1664,19 @@
       <c r="N24" s="23">
         <v>37.932834522359492</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O24" s="12">
+        <v>44.506936632920883</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D25" s="2">
         <v>10.3</v>
@@ -1646,16 +1711,19 @@
       <c r="N25" s="23">
         <v>26.985549456704376</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O25" s="12">
+        <v>30.885265884504037</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D26" s="8">
         <v>12.5</v>
@@ -1690,16 +1758,19 @@
       <c r="N26" s="22">
         <v>27.190143693828379</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O26" s="11">
+        <v>29.408125819134995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D27" s="2">
         <v>24.3</v>
@@ -1734,16 +1805,19 @@
       <c r="N27" s="23">
         <v>54.006768771869439</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O27" s="12">
+        <v>48.114630467571644</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D28" s="2">
         <v>9.3000000000000007</v>
@@ -1778,16 +1852,19 @@
       <c r="N28" s="23">
         <v>22.334624692306893</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O28" s="12">
+        <v>25.085835247954151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D29" s="8">
         <v>31</v>
@@ -1822,16 +1899,19 @@
       <c r="N29" s="22">
         <v>36.01461582008131</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O29" s="11">
+        <v>39.199494735254468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D30" s="6">
         <v>41.9</v>
@@ -1865,6 +1945,9 @@
       </c>
       <c r="N30" s="21">
         <v>42.081208505725009</v>
+      </c>
+      <c r="O30" s="13">
+        <v>40.756671840810903</v>
       </c>
     </row>
   </sheetData>
